--- a/data/Paper evaluations.xlsx
+++ b/data/Paper evaluations.xlsx
@@ -9,26 +9,27 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="6280" windowHeight="5700" firstSheet="3" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="6280" windowHeight="5700" firstSheet="6" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="ablation" sheetId="3" r:id="rId3"/>
     <sheet name="eval results" sheetId="9" r:id="rId4"/>
-    <sheet name="choosing signal family" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
-    <sheet name="choosing strongest meta" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId8"/>
-    <sheet name="decide best meta model" sheetId="8" r:id="rId9"/>
+    <sheet name="Runtime latency" sheetId="10" r:id="rId5"/>
+    <sheet name="choosing signal family" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId7"/>
+    <sheet name="choosing strongest meta" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId9"/>
+    <sheet name="decide best meta model" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Sheet4!$A$1:$H$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Sheet4!$A$1:$H$190</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId10"/>
-    <pivotCache cacheId="1" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="187">
   <si>
     <t>ML Algorithms</t>
   </si>
@@ -544,6 +545,63 @@
   <si>
     <t>Error %</t>
   </si>
+  <si>
+    <t>Analysis Type</t>
+  </si>
+  <si>
+    <t>VT Mode</t>
+  </si>
+  <si>
+    <t>normalization_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>tranco_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>vt_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>bert_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>catboost_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>final_meta_model_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>full_pipeline_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>decision_only_average_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>decision_only_meta_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>cached</t>
+  </si>
+  <si>
+    <t>precomputed_states</t>
+  </si>
+  <si>
+    <t>uncached</t>
+  </si>
+  <si>
+    <t>150 samples</t>
+  </si>
+  <si>
+    <t>Meta-model</t>
+  </si>
+  <si>
+    <t>avg_fusion_avg_time_per_url_s</t>
+  </si>
+  <si>
+    <t>Full pipeline</t>
+  </si>
+  <si>
+    <t>Decision only</t>
+  </si>
 </sst>
 </file>
 
@@ -690,7 +748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -709,6 +767,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -721,16 +786,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2997,7 +3060,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6054,7 +6116,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14102,13 +14163,13 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C2" s="3"/>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
@@ -14503,14 +14564,14 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C24" s="5"/>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
@@ -15169,6 +15230,1885 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U64"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="13" max="13" width="18.08984375" customWidth="1"/>
+    <col min="14" max="14" width="15.26953125" customWidth="1"/>
+    <col min="15" max="20" width="7.81640625" customWidth="1"/>
+    <col min="21" max="22" width="11.81640625" customWidth="1"/>
+    <col min="23" max="28" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.99209999999999998</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.99760000000000004</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.99480000000000002</v>
+      </c>
+      <c r="H2" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.98819999999999997</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.98960000000000004</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.99019999999999997</v>
+      </c>
+      <c r="H3" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.99350000000000005</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.99160000000000004</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.99760000000000004</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.99460000000000004</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.98860000000000003</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.98429999999999995</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.99690000000000001</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.99060000000000004</v>
+      </c>
+      <c r="H5" s="6">
+        <v>2E-3</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="N5" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P5" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5" t="s">
+        <v>106</v>
+      </c>
+      <c r="S5" t="s">
+        <v>107</v>
+      </c>
+      <c r="T5" t="s">
+        <v>108</v>
+      </c>
+      <c r="U5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.98870000000000002</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.98350000000000004</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.99790000000000001</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="H6" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0.99480000000000002</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0.99019999999999997</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0.99460000000000004</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0.99060000000000004</v>
+      </c>
+      <c r="R6" s="11">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="S6" s="11">
+        <v>0.9909</v>
+      </c>
+      <c r="T6" s="11">
+        <v>0.99450000000000005</v>
+      </c>
+      <c r="U6" s="11">
+        <v>0.99232857142857156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.98419999999999996</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.99780000000000002</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.9909</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0.99339999999999995</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="P7" s="11">
+        <v>0.99370000000000003</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="R7" s="11">
+        <v>0.99</v>
+      </c>
+      <c r="S7" s="11">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="T7" s="11">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="U7" s="11">
+        <v>0.99154285714285717</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.99329999999999996</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.99229999999999996</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.99670000000000003</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.99450000000000005</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0.9909</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0.99319999999999997</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0.98719999999999997</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0.98919999999999997</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0.98909999999999998</v>
+      </c>
+      <c r="T8" s="11">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="U8" s="11">
+        <v>0.99102857142857137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.99709999999999999</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.99339999999999995</v>
+      </c>
+      <c r="H9" s="6">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0.99119999999999997</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0.9909</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0.99160000000000004</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0.98740000000000006</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0.98729999999999996</v>
+      </c>
+      <c r="S9" s="11">
+        <v>0.9889</v>
+      </c>
+      <c r="T9" s="11">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="U9" s="11">
+        <v>0.98977142857142864</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.98929999999999996</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2E-3</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0.99339999999999995</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0.99350000000000005</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0.99050000000000005</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0.99050000000000005</v>
+      </c>
+      <c r="S10" s="11">
+        <v>0.99129999999999996</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0.99360000000000004</v>
+      </c>
+      <c r="U10" s="11">
+        <v>0.99184285714285714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.99639999999999995</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.99370000000000003</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.99332000000000009</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0.99063999999999997</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0.99331999999999998</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0.98916000000000004</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0.98954000000000009</v>
+      </c>
+      <c r="S11" s="11">
+        <v>0.99006000000000005</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0.99307999999999996</v>
+      </c>
+      <c r="U11" s="11">
+        <v>0.99130285714285715</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.9879</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.98309999999999997</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.99709999999999999</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="H12" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.98780000000000001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.99709999999999999</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="H13" s="6">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.9879</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.98350000000000004</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.99670000000000003</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.27300000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.9909</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.99519999999999997</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.7429</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.75460000000000005</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="H16" s="6">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.71330000000000005</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.79610000000000003</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.70409999999999995</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.74729999999999996</v>
+      </c>
+      <c r="H17" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.74270000000000003</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.75649999999999995</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0.84430000000000005</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="H18" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.56579999999999997</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.60370000000000001</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.81130000000000002</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0.69230000000000003</v>
+      </c>
+      <c r="H19" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.7319</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.7258</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.89139999999999997</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0.80010000000000003</v>
+      </c>
+      <c r="H20" s="6">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.71460000000000001</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.68379999999999996</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.97840000000000005</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="H21" s="6">
+        <v>5.0789999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.74170000000000003</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.75870000000000004</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="H22" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.99250000000000005</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.9909</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.99670000000000003</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="H23" s="6">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.99019999999999997</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0.9909</v>
+      </c>
+      <c r="H24" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.99180000000000001</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.99039999999999995</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0.996</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0.99319999999999997</v>
+      </c>
+      <c r="H25" s="6">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.98450000000000004</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.97940000000000005</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.99519999999999997</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.98719999999999997</v>
+      </c>
+      <c r="H26" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.98680000000000001</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.97889999999999999</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0.98919999999999997</v>
+      </c>
+      <c r="H27" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.98670000000000002</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.97870000000000001</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0.98909999999999998</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0.51800000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.99250000000000005</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.99650000000000005</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="H29" s="6">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.85740000000000005</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.8528</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0.92230000000000001</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0.88619999999999999</v>
+      </c>
+      <c r="H30" s="6">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.88819999999999999</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.89790000000000003</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.91869999999999996</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0.90820000000000001</v>
+      </c>
+      <c r="H31" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.85209999999999997</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0.93269999999999997</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0.89059999999999995</v>
+      </c>
+      <c r="H32" s="6">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.4239</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.5272</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="G33" s="6">
+        <v>0.46550000000000002</v>
+      </c>
+      <c r="H33" s="6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0.91390000000000005</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0.87649999999999995</v>
+      </c>
+      <c r="H34" s="6">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.82120000000000004</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="H35" s="6">
+        <v>4.5759999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.86029999999999995</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.92020000000000002</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0.8881</v>
+      </c>
+      <c r="H36" s="6">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0.98939999999999995</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0.99450000000000005</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.99119999999999997</v>
+      </c>
+      <c r="H37" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.98919999999999997</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0.99260000000000004</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0.9909</v>
+      </c>
+      <c r="H38" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.98980000000000001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.98570000000000002</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0.99760000000000004</v>
+      </c>
+      <c r="G39" s="6">
+        <v>0.99160000000000004</v>
+      </c>
+      <c r="H39" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.98460000000000003</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.97540000000000004</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0.98740000000000006</v>
+      </c>
+      <c r="H40" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.98450000000000004</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.97519999999999996</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0.98729999999999996</v>
+      </c>
+      <c r="H41" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.98650000000000004</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.9798</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="G42" s="6">
+        <v>0.9889</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0.247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.98919999999999997</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.98729999999999996</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0.99480000000000002</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0.99109999999999998</v>
+      </c>
+      <c r="H43" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.99019999999999997</v>
+      </c>
+      <c r="F44" s="6">
+        <v>0.99650000000000005</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0.99339999999999995</v>
+      </c>
+      <c r="H44" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.99029999999999996</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0.98980000000000001</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="H45" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0.99219999999999997</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0.99639999999999995</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0.99350000000000005</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0.98850000000000005</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.98419999999999996</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0.99690000000000001</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0.99050000000000005</v>
+      </c>
+      <c r="H47" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.98850000000000005</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.98319999999999996</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0.99790000000000001</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0.99050000000000005</v>
+      </c>
+      <c r="H48" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0.98950000000000005</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.98450000000000004</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0.99829999999999997</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0.99129999999999996</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.99229999999999996</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.99119999999999997</v>
+      </c>
+      <c r="F50" s="6">
+        <v>0.996</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0.99360000000000004</v>
+      </c>
+      <c r="H50" s="6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.87190000000000001</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.8669</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0.92989999999999995</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0.89729999999999999</v>
+      </c>
+      <c r="H51" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0.84640000000000004</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="F52" s="6">
+        <v>0.88119999999999998</v>
+      </c>
+      <c r="G52" s="6">
+        <v>0.87350000000000005</v>
+      </c>
+      <c r="H52" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="6">
+        <v>0.8679</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0.85840000000000005</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="H53" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="6">
+        <v>0.5615</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0.60129999999999995</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0.80559999999999998</v>
+      </c>
+      <c r="G54" s="6">
+        <v>0.68869999999999998</v>
+      </c>
+      <c r="H54" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0.85609999999999997</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0.85129999999999995</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="G55" s="6">
+        <v>0.88519999999999999</v>
+      </c>
+      <c r="H55" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" s="6">
+        <v>0.80489999999999995</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0.81559999999999999</v>
+      </c>
+      <c r="F56" s="6">
+        <v>0.87350000000000005</v>
+      </c>
+      <c r="G56" s="6">
+        <v>0.84350000000000003</v>
+      </c>
+      <c r="H56" s="6">
+        <v>4.3010000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0.86709999999999998</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.86650000000000005</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0.92110000000000003</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="H57" s="6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.82979999999999998</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.82350000000000001</v>
+      </c>
+      <c r="F58" s="6">
+        <v>0.91279999999999994</v>
+      </c>
+      <c r="G58" s="6">
+        <v>0.8659</v>
+      </c>
+      <c r="H58" s="6">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.82150000000000001</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.84419999999999995</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0.86260000000000003</v>
+      </c>
+      <c r="G59" s="6">
+        <v>0.85329999999999995</v>
+      </c>
+      <c r="H59" s="6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" s="6">
+        <v>0.8306</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.82040000000000002</v>
+      </c>
+      <c r="F60" s="6">
+        <v>0.92010000000000003</v>
+      </c>
+      <c r="G60" s="6">
+        <v>0.86739999999999995</v>
+      </c>
+      <c r="H60" s="6">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0.58130000000000004</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0.61009999999999998</v>
+      </c>
+      <c r="F61" s="6">
+        <v>0.84379999999999999</v>
+      </c>
+      <c r="G61" s="6">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="H61" s="6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D62" s="6">
+        <v>0.81469999999999998</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.8115</v>
+      </c>
+      <c r="F62" s="6">
+        <v>0.90159999999999996</v>
+      </c>
+      <c r="G62" s="6">
+        <v>0.85419999999999996</v>
+      </c>
+      <c r="H62" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0.79139999999999999</v>
+      </c>
+      <c r="E63" s="6">
+        <v>0.79549999999999998</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0.87970000000000004</v>
+      </c>
+      <c r="G63" s="6">
+        <v>0.83550000000000002</v>
+      </c>
+      <c r="H63" s="6">
+        <v>5.1920000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64" s="6">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0.82809999999999995</v>
+      </c>
+      <c r="F64" s="6">
+        <v>0.8992</v>
+      </c>
+      <c r="G64" s="6">
+        <v>0.86219999999999997</v>
+      </c>
+      <c r="H64" s="6">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -21908,20 +23848,20 @@
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="18" customWidth="1"/>
-    <col min="5" max="6" width="8.7265625" style="18"/>
-    <col min="7" max="7" width="13.08984375" style="18" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="18"/>
+    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="14" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="14"/>
+    <col min="7" max="7" width="13.08984375" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
         <v>150</v>
       </c>
     </row>
@@ -21932,88 +23872,88 @@
       <c r="B3" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="17" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="15">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="15">
         <v>0</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <v>0</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -22022,285 +23962,285 @@
       <c r="B10" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="17" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="15">
         <v>0.98876404494381998</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="15">
         <v>0.99435028248587498</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="15">
         <v>14.63</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="15">
         <v>9.7530000000000006E-2</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="15">
         <v>0.98876404494381998</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="15">
         <v>0.99435028248587498</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="15">
         <v>13.551</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="15">
         <v>9.0340000000000004E-2</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="15">
         <v>0</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="15">
         <v>0</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="15">
         <v>13.884</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="15">
         <v>9.2560000000000003E-2</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="19" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="15">
         <v>0</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="15">
         <v>0</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="15">
         <v>14.234</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="15">
         <v>9.4890000000000002E-2</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="15">
         <v>20.207999999999998</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="15">
         <v>0.13472000000000001</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="15">
         <v>18.305</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="15">
         <v>0.12203</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
-      <c r="B17" s="19" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="15">
         <v>0</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="15">
         <v>0</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="15">
         <v>17.940000000000001</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="15">
         <v>0.1196</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="B18" s="19" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="15">
         <v>0</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="15">
         <v>0</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="15">
         <v>17.780999999999999</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="15">
         <v>0.11854000000000001</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="15">
         <v>1</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="15">
         <v>1</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="15">
         <v>17.846</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="15">
         <v>0.11897000000000001</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
-      <c r="B20" s="19" t="s">
+      <c r="A20" s="25"/>
+      <c r="B20" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="15">
         <v>18.495000000000001</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="15">
         <v>0.12330000000000001</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="25"/>
+      <c r="B21" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="15">
         <v>0</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="15">
         <v>0</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="15">
         <v>18.853000000000002</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="15">
         <v>0.12569</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="19" t="s">
+      <c r="A22" s="25"/>
+      <c r="B22" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="15">
         <v>0</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="15">
         <v>0</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="15">
         <v>18.791</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="15">
         <v>0.12528</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="15">
         <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="16" t="s">
         <v>150</v>
       </c>
     </row>
@@ -22308,144 +24248,144 @@
       <c r="A26" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="I26" s="22" t="s">
+      <c r="I26" s="17" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="15">
         <v>2.3499999999999999E-4</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="19">
         <v>6.9999999999999999E-6</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="15">
         <v>8.6899999999999998E-4</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="15">
         <v>8.9820999999999998E-2</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="15">
         <v>4.3730000000000002E-3</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="15">
         <v>3.8059999999999999E-3</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="15">
         <v>9.9139000000000005E-2</v>
       </c>
-      <c r="I27" s="19"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="15">
         <v>2.32E-4</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="19">
         <v>1.1E-5</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="15">
         <v>1.3110000000000001E-3</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="15">
         <v>0.114466</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="15">
         <v>5.672E-3</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="15">
         <v>5.3870000000000003E-3</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="15">
         <v>0.12712100000000001</v>
       </c>
-      <c r="I29" s="19"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="20"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="15">
         <v>2.8200000000000002E-4</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="19">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="15">
         <v>1.2160000000000001E-3</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="15">
         <v>0.112817</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="15">
         <v>5.738E-3</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="15">
         <v>5.5770000000000004E-3</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="15">
         <v>0.12567800000000001</v>
       </c>
-      <c r="I31" s="19"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="20"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -22461,6 +24401,332 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" customWidth="1"/>
+    <col min="9" max="9" width="10.90625" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="M2" s="28" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3">
+        <v>3.4600000000000001E-4</v>
+      </c>
+      <c r="E3" s="26">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="F3">
+        <v>1.16E-3</v>
+      </c>
+      <c r="G3">
+        <v>0.11007400000000001</v>
+      </c>
+      <c r="H3">
+        <v>5.62E-3</v>
+      </c>
+      <c r="I3" s="26">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J3">
+        <v>5.012E-3</v>
+      </c>
+      <c r="K3">
+        <v>0.12225900000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="26">
+        <v>3.1999999999999999E-5</v>
+      </c>
+      <c r="E4" s="26">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="F4">
+        <v>14.813259</v>
+      </c>
+      <c r="G4">
+        <v>8.5699999999999998E-2</v>
+      </c>
+      <c r="H4">
+        <v>3.9690000000000003E-3</v>
+      </c>
+      <c r="I4" s="26">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="J4">
+        <v>3.1700000000000001E-3</v>
+      </c>
+      <c r="K4">
+        <v>14.906174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="L5" s="26">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="M5">
+        <v>2.4060000000000002E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>2.2599999999999999E-4</v>
+      </c>
+      <c r="E6" s="26">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="F6">
+        <v>1E-3</v>
+      </c>
+      <c r="G6">
+        <v>8.7034E-2</v>
+      </c>
+      <c r="H6">
+        <v>4.248E-3</v>
+      </c>
+      <c r="I6" s="26">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="J6">
+        <v>4.4079999999999996E-3</v>
+      </c>
+      <c r="K6">
+        <v>9.6950999999999996E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="26">
+        <v>3.6000000000000001E-5</v>
+      </c>
+      <c r="E7" s="26">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="F7">
+        <v>14.917517999999999</v>
+      </c>
+      <c r="G7">
+        <v>8.4262000000000004E-2</v>
+      </c>
+      <c r="H7">
+        <v>4.0299999999999997E-3</v>
+      </c>
+      <c r="I7" s="26">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="J7">
+        <v>3.6840000000000002E-3</v>
+      </c>
+      <c r="K7">
+        <v>15.009575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="L8" s="26">
+        <v>1.4E-5</v>
+      </c>
+      <c r="M8">
+        <v>4.9410000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9">
+        <v>2.41E-4</v>
+      </c>
+      <c r="E9" s="26">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="F9">
+        <v>1.023E-3</v>
+      </c>
+      <c r="G9">
+        <v>9.2588000000000004E-2</v>
+      </c>
+      <c r="H9">
+        <v>5.0410000000000003E-3</v>
+      </c>
+      <c r="I9" s="26">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J9">
+        <v>1.0697999999999999E-2</v>
+      </c>
+      <c r="K9">
+        <v>0.10963199999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="26">
+        <v>2.8E-5</v>
+      </c>
+      <c r="E10" s="26">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="F10">
+        <v>14.823589</v>
+      </c>
+      <c r="G10">
+        <v>7.9023999999999997E-2</v>
+      </c>
+      <c r="H10">
+        <v>3.7490000000000002E-3</v>
+      </c>
+      <c r="I10" s="26">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="J10">
+        <v>3.2299999999999998E-3</v>
+      </c>
+      <c r="K10">
+        <v>14.909662000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="L11" s="26">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="M11">
+        <v>2.0690000000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:J61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -22834,7 +25100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -23077,7 +25343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -24006,7 +26272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H190"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -28963,1883 +31229,4 @@
   <autoFilter ref="A1:H190"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U64"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="13" max="13" width="18.08984375" customWidth="1"/>
-    <col min="14" max="14" width="15.26953125" customWidth="1"/>
-    <col min="15" max="20" width="7.81640625" customWidth="1"/>
-    <col min="21" max="22" width="11.81640625" customWidth="1"/>
-    <col min="23" max="28" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="30.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0.99209999999999998</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.99760000000000004</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0.99480000000000002</v>
-      </c>
-      <c r="H2" s="6">
-        <v>8.9999999999999993E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.98819999999999997</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.99070000000000003</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.98960000000000004</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0.99019999999999997</v>
-      </c>
-      <c r="H3" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0.99350000000000005</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.99160000000000004</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.99760000000000004</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0.99460000000000004</v>
-      </c>
-      <c r="H4" s="6">
-        <v>1.2E-2</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0.98860000000000003</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.98429999999999995</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.99690000000000001</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.99060000000000004</v>
-      </c>
-      <c r="H5" s="6">
-        <v>2E-3</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P5" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>105</v>
-      </c>
-      <c r="R5" t="s">
-        <v>106</v>
-      </c>
-      <c r="S5" t="s">
-        <v>107</v>
-      </c>
-      <c r="T5" t="s">
-        <v>108</v>
-      </c>
-      <c r="U5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0.98870000000000002</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.98350000000000004</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.99790000000000001</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0.99070000000000003</v>
-      </c>
-      <c r="H6" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="N6" s="11">
-        <v>0.99480000000000002</v>
-      </c>
-      <c r="O6" s="11">
-        <v>0.99019999999999997</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0.99460000000000004</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0.99060000000000004</v>
-      </c>
-      <c r="R6" s="11">
-        <v>0.99070000000000003</v>
-      </c>
-      <c r="S6" s="11">
-        <v>0.9909</v>
-      </c>
-      <c r="T6" s="11">
-        <v>0.99450000000000005</v>
-      </c>
-      <c r="U6" s="11">
-        <v>0.99232857142857156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.98419999999999996</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.99780000000000002</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.9909</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0.99339999999999995</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0.99109999999999998</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0.99370000000000003</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>0.99009999999999998</v>
-      </c>
-      <c r="R7" s="11">
-        <v>0.99</v>
-      </c>
-      <c r="S7" s="11">
-        <v>0.99009999999999998</v>
-      </c>
-      <c r="T7" s="11">
-        <v>0.99239999999999995</v>
-      </c>
-      <c r="U7" s="11">
-        <v>0.99154285714285717</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0.99329999999999996</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.99229999999999996</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.99670000000000003</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.99450000000000005</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="O8" s="11">
-        <v>0.9909</v>
-      </c>
-      <c r="P8" s="11">
-        <v>0.99319999999999997</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0.98719999999999997</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0.98919999999999997</v>
-      </c>
-      <c r="S8" s="11">
-        <v>0.98909999999999998</v>
-      </c>
-      <c r="T8" s="11">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="U8" s="11">
-        <v>0.99102857142857137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.98970000000000002</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.99709999999999999</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.99339999999999995</v>
-      </c>
-      <c r="H9" s="6">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0.99119999999999997</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0.9909</v>
-      </c>
-      <c r="P9" s="11">
-        <v>0.99160000000000004</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0.98740000000000006</v>
-      </c>
-      <c r="R9" s="11">
-        <v>0.98729999999999996</v>
-      </c>
-      <c r="S9" s="11">
-        <v>0.9889</v>
-      </c>
-      <c r="T9" s="11">
-        <v>0.99109999999999998</v>
-      </c>
-      <c r="U9" s="11">
-        <v>0.98977142857142864</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.98929999999999996</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.99150000000000005</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.99070000000000003</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0.99109999999999998</v>
-      </c>
-      <c r="H10" s="6">
-        <v>2E-3</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="N10" s="11">
-        <v>0.99339999999999995</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0.99009999999999998</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0.99350000000000005</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0.99050000000000005</v>
-      </c>
-      <c r="R10" s="11">
-        <v>0.99050000000000005</v>
-      </c>
-      <c r="S10" s="11">
-        <v>0.99129999999999996</v>
-      </c>
-      <c r="T10" s="11">
-        <v>0.99360000000000004</v>
-      </c>
-      <c r="U10" s="11">
-        <v>0.99184285714285714</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.99239999999999995</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.99109999999999998</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.99639999999999995</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.99370000000000003</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1.2E-2</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0.99332000000000009</v>
-      </c>
-      <c r="O11" s="11">
-        <v>0.99063999999999997</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0.99331999999999998</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>0.98916000000000004</v>
-      </c>
-      <c r="R11" s="11">
-        <v>0.98954000000000009</v>
-      </c>
-      <c r="S11" s="11">
-        <v>0.99006000000000005</v>
-      </c>
-      <c r="T11" s="11">
-        <v>0.99307999999999996</v>
-      </c>
-      <c r="U11" s="11">
-        <v>0.99130285714285715</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.9879</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.98309999999999997</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.99709999999999999</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.99009999999999998</v>
-      </c>
-      <c r="H12" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.98780000000000001</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.99709999999999999</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0.99</v>
-      </c>
-      <c r="H13" s="6">
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.9879</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.98350000000000004</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.99670000000000003</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.99009999999999998</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0.27300000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.9909</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.98970000000000002</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.99519999999999997</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.99239999999999995</v>
-      </c>
-      <c r="H15" s="6">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.7429</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.75460000000000005</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0.79900000000000004</v>
-      </c>
-      <c r="H16" s="6">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.71330000000000005</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.79610000000000003</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.70409999999999995</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0.74729999999999996</v>
-      </c>
-      <c r="H17" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.74270000000000003</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.75649999999999995</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0.84430000000000005</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="H18" s="6">
-        <v>8.9999999999999993E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.56579999999999997</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.60370000000000001</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0.81130000000000002</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0.69230000000000003</v>
-      </c>
-      <c r="H19" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.7319</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.7258</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0.89139999999999997</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0.80010000000000003</v>
-      </c>
-      <c r="H20" s="6">
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0.71460000000000001</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.68379999999999996</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0.97840000000000005</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0.80500000000000005</v>
-      </c>
-      <c r="H21" s="6">
-        <v>5.0789999999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.74170000000000003</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.75870000000000004</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0.79600000000000004</v>
-      </c>
-      <c r="H22" s="6">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.99250000000000005</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.9909</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.99670000000000003</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="H23" s="6">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.99019999999999997</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0.99150000000000005</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0.9909</v>
-      </c>
-      <c r="H24" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0.99180000000000001</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.99039999999999995</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0.996</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0.99319999999999997</v>
-      </c>
-      <c r="H25" s="6">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0.98450000000000004</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.97940000000000005</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0.99519999999999997</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0.98719999999999997</v>
-      </c>
-      <c r="H26" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0.98680000000000001</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.97889999999999999</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0.99970000000000003</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0.98919999999999997</v>
-      </c>
-      <c r="H27" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0.98670000000000002</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.97870000000000001</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0.99970000000000003</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0.98909999999999998</v>
-      </c>
-      <c r="H28" s="6">
-        <v>0.51800000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0.99250000000000005</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.99109999999999998</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0.99650000000000005</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="H29" s="6">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0.85740000000000005</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.8528</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0.92230000000000001</v>
-      </c>
-      <c r="G30" s="6">
-        <v>0.88619999999999999</v>
-      </c>
-      <c r="H30" s="6">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" s="6">
-        <v>0.88819999999999999</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.89790000000000003</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0.91869999999999996</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0.90820000000000001</v>
-      </c>
-      <c r="H31" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.85209999999999997</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0.93269999999999997</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0.89059999999999995</v>
-      </c>
-      <c r="H32" s="6">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="6">
-        <v>0.4239</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.5272</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0.41670000000000001</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0.46550000000000002</v>
-      </c>
-      <c r="H33" s="6">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" s="6">
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.84209999999999996</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0.91390000000000005</v>
-      </c>
-      <c r="G34" s="6">
-        <v>0.87649999999999995</v>
-      </c>
-      <c r="H34" s="6">
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" s="6">
-        <v>0.81899999999999995</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.82120000000000004</v>
-      </c>
-      <c r="F35" s="6">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="G35" s="6">
-        <v>0.85599999999999998</v>
-      </c>
-      <c r="H35" s="6">
-        <v>4.5759999999999996</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="6">
-        <v>0.86029999999999995</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.85799999999999998</v>
-      </c>
-      <c r="F36" s="6">
-        <v>0.92020000000000002</v>
-      </c>
-      <c r="G36" s="6">
-        <v>0.8881</v>
-      </c>
-      <c r="H36" s="6">
-        <v>2.4E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="6">
-        <v>0.98939999999999995</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="F37" s="6">
-        <v>0.99450000000000005</v>
-      </c>
-      <c r="G37" s="6">
-        <v>0.99119999999999997</v>
-      </c>
-      <c r="H37" s="6">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="6">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.98919999999999997</v>
-      </c>
-      <c r="F38" s="6">
-        <v>0.99260000000000004</v>
-      </c>
-      <c r="G38" s="6">
-        <v>0.9909</v>
-      </c>
-      <c r="H38" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39" s="6">
-        <v>0.98980000000000001</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.98570000000000002</v>
-      </c>
-      <c r="F39" s="6">
-        <v>0.99760000000000004</v>
-      </c>
-      <c r="G39" s="6">
-        <v>0.99160000000000004</v>
-      </c>
-      <c r="H39" s="6">
-        <v>8.9999999999999993E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="6">
-        <v>0.98460000000000003</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.97540000000000004</v>
-      </c>
-      <c r="F40" s="6">
-        <v>0.99970000000000003</v>
-      </c>
-      <c r="G40" s="6">
-        <v>0.98740000000000006</v>
-      </c>
-      <c r="H40" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="6">
-        <v>0.98450000000000004</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.97519999999999996</v>
-      </c>
-      <c r="F41" s="6">
-        <v>0.99970000000000003</v>
-      </c>
-      <c r="G41" s="6">
-        <v>0.98729999999999996</v>
-      </c>
-      <c r="H41" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42" s="6">
-        <v>0.98650000000000004</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.9798</v>
-      </c>
-      <c r="F42" s="6">
-        <v>0.99809999999999999</v>
-      </c>
-      <c r="G42" s="6">
-        <v>0.9889</v>
-      </c>
-      <c r="H42" s="6">
-        <v>0.247</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" s="6">
-        <v>0.98919999999999997</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.98729999999999996</v>
-      </c>
-      <c r="F43" s="6">
-        <v>0.99480000000000002</v>
-      </c>
-      <c r="G43" s="6">
-        <v>0.99109999999999998</v>
-      </c>
-      <c r="H43" s="6">
-        <v>1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="6">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.99019999999999997</v>
-      </c>
-      <c r="F44" s="6">
-        <v>0.99650000000000005</v>
-      </c>
-      <c r="G44" s="6">
-        <v>0.99339999999999995</v>
-      </c>
-      <c r="H44" s="6">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" s="6">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.99029999999999996</v>
-      </c>
-      <c r="F45" s="6">
-        <v>0.98980000000000001</v>
-      </c>
-      <c r="G45" s="6">
-        <v>0.99009999999999998</v>
-      </c>
-      <c r="H45" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" s="6">
-        <v>0.99219999999999997</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.99070000000000003</v>
-      </c>
-      <c r="F46" s="6">
-        <v>0.99639999999999995</v>
-      </c>
-      <c r="G46" s="6">
-        <v>0.99350000000000005</v>
-      </c>
-      <c r="H46" s="6">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" s="6">
-        <v>0.98850000000000005</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.98419999999999996</v>
-      </c>
-      <c r="F47" s="6">
-        <v>0.99690000000000001</v>
-      </c>
-      <c r="G47" s="6">
-        <v>0.99050000000000005</v>
-      </c>
-      <c r="H47" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" s="6">
-        <v>0.98850000000000005</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.98319999999999996</v>
-      </c>
-      <c r="F48" s="6">
-        <v>0.99790000000000001</v>
-      </c>
-      <c r="G48" s="6">
-        <v>0.99050000000000005</v>
-      </c>
-      <c r="H48" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" s="6">
-        <v>0.98950000000000005</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.98450000000000004</v>
-      </c>
-      <c r="F49" s="6">
-        <v>0.99829999999999997</v>
-      </c>
-      <c r="G49" s="6">
-        <v>0.99129999999999996</v>
-      </c>
-      <c r="H49" s="6">
-        <v>0.22500000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="6">
-        <v>0.99229999999999996</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.99119999999999997</v>
-      </c>
-      <c r="F50" s="6">
-        <v>0.996</v>
-      </c>
-      <c r="G50" s="6">
-        <v>0.99360000000000004</v>
-      </c>
-      <c r="H50" s="6">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" s="6">
-        <v>0.87190000000000001</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.8669</v>
-      </c>
-      <c r="F51" s="6">
-        <v>0.92989999999999995</v>
-      </c>
-      <c r="G51" s="6">
-        <v>0.89729999999999999</v>
-      </c>
-      <c r="H51" s="6">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" s="6">
-        <v>0.84640000000000004</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.86599999999999999</v>
-      </c>
-      <c r="F52" s="6">
-        <v>0.88119999999999998</v>
-      </c>
-      <c r="G52" s="6">
-        <v>0.87350000000000005</v>
-      </c>
-      <c r="H52" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" s="6">
-        <v>0.8679</v>
-      </c>
-      <c r="E53" s="6">
-        <v>0.85840000000000005</v>
-      </c>
-      <c r="F53" s="6">
-        <v>0.93469999999999998</v>
-      </c>
-      <c r="G53" s="6">
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="H53" s="6">
-        <v>8.9999999999999993E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D54" s="6">
-        <v>0.5615</v>
-      </c>
-      <c r="E54" s="6">
-        <v>0.60129999999999995</v>
-      </c>
-      <c r="F54" s="6">
-        <v>0.80559999999999998</v>
-      </c>
-      <c r="G54" s="6">
-        <v>0.68869999999999998</v>
-      </c>
-      <c r="H54" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" s="6">
-        <v>0.85609999999999997</v>
-      </c>
-      <c r="E55" s="6">
-        <v>0.85129999999999995</v>
-      </c>
-      <c r="F55" s="6">
-        <v>0.92200000000000004</v>
-      </c>
-      <c r="G55" s="6">
-        <v>0.88519999999999999</v>
-      </c>
-      <c r="H55" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D56" s="6">
-        <v>0.80489999999999995</v>
-      </c>
-      <c r="E56" s="6">
-        <v>0.81559999999999999</v>
-      </c>
-      <c r="F56" s="6">
-        <v>0.87350000000000005</v>
-      </c>
-      <c r="G56" s="6">
-        <v>0.84350000000000003</v>
-      </c>
-      <c r="H56" s="6">
-        <v>4.3010000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" s="6">
-        <v>0.86709999999999998</v>
-      </c>
-      <c r="E57" s="6">
-        <v>0.86650000000000005</v>
-      </c>
-      <c r="F57" s="6">
-        <v>0.92110000000000003</v>
-      </c>
-      <c r="G57" s="6">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="H57" s="6">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="6">
-        <v>0.82979999999999998</v>
-      </c>
-      <c r="E58" s="6">
-        <v>0.82350000000000001</v>
-      </c>
-      <c r="F58" s="6">
-        <v>0.91279999999999994</v>
-      </c>
-      <c r="G58" s="6">
-        <v>0.8659</v>
-      </c>
-      <c r="H58" s="6">
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" s="6">
-        <v>0.82150000000000001</v>
-      </c>
-      <c r="E59" s="6">
-        <v>0.84419999999999995</v>
-      </c>
-      <c r="F59" s="6">
-        <v>0.86260000000000003</v>
-      </c>
-      <c r="G59" s="6">
-        <v>0.85329999999999995</v>
-      </c>
-      <c r="H59" s="6">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" s="6">
-        <v>0.8306</v>
-      </c>
-      <c r="E60" s="6">
-        <v>0.82040000000000002</v>
-      </c>
-      <c r="F60" s="6">
-        <v>0.92010000000000003</v>
-      </c>
-      <c r="G60" s="6">
-        <v>0.86739999999999995</v>
-      </c>
-      <c r="H60" s="6">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" s="6">
-        <v>0.58130000000000004</v>
-      </c>
-      <c r="E61" s="6">
-        <v>0.61009999999999998</v>
-      </c>
-      <c r="F61" s="6">
-        <v>0.84379999999999999</v>
-      </c>
-      <c r="G61" s="6">
-        <v>0.70809999999999995</v>
-      </c>
-      <c r="H61" s="6">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62" s="6">
-        <v>0.81469999999999998</v>
-      </c>
-      <c r="E62" s="6">
-        <v>0.8115</v>
-      </c>
-      <c r="F62" s="6">
-        <v>0.90159999999999996</v>
-      </c>
-      <c r="G62" s="6">
-        <v>0.85419999999999996</v>
-      </c>
-      <c r="H62" s="6">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D63" s="6">
-        <v>0.79139999999999999</v>
-      </c>
-      <c r="E63" s="6">
-        <v>0.79549999999999998</v>
-      </c>
-      <c r="F63" s="6">
-        <v>0.87970000000000004</v>
-      </c>
-      <c r="G63" s="6">
-        <v>0.83550000000000002</v>
-      </c>
-      <c r="H63" s="6">
-        <v>5.1920000000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D64" s="6">
-        <v>0.82699999999999996</v>
-      </c>
-      <c r="E64" s="6">
-        <v>0.82809999999999995</v>
-      </c>
-      <c r="F64" s="6">
-        <v>0.8992</v>
-      </c>
-      <c r="G64" s="6">
-        <v>0.86219999999999997</v>
-      </c>
-      <c r="H64" s="6">
-        <v>8.9999999999999993E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>